--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 70 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 67 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6775,8 +6775,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8100,8 +8100,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -20074,7 +20074,7 @@
         </is>
       </c>
       <c r="P189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q189" s="9" t="n">
         <v>0</v>
@@ -21426,7 +21426,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21888,7 +21888,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,11 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3080,7 +3084,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3492,7 +3500,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3698,7 +3710,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4005,7 +4021,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4106,7 +4126,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -8214,7 +8238,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8630,7 +8658,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9450,7 +9482,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9757,7 +9793,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -10884,7 +10924,11 @@
       <c r="AB99" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11090,7 +11134,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11397,7 +11445,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -12217,7 +12269,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12629,7 +12685,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12831,7 +12891,11 @@
       <c r="AB118" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC118" s="4" t="inlineStr"/>
+      <c r="AC118" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -13857,7 +13921,11 @@
       <c r="AB128" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14879,7 +14947,11 @@
       <c r="AB138" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -15392,7 +15464,11 @@
       <c r="AB143" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC143" s="4" t="inlineStr"/>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -16618,7 +16694,11 @@
       <c r="AB155" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -16719,7 +16799,11 @@
       <c r="AB156" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC156" s="4" t="inlineStr"/>
+      <c r="AC156" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -17127,7 +17211,11 @@
       <c r="AB160" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC160" s="4" t="inlineStr"/>
+      <c r="AC160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -18262,7 +18350,11 @@
       <c r="AB171" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -19094,7 +19186,11 @@
       <c r="AB179" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC179" s="4" t="inlineStr"/>
+      <c r="AC179" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -19300,7 +19396,11 @@
       <c r="AB181" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC181" s="4" t="inlineStr"/>
+      <c r="AC181" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19506,7 +19606,11 @@
       <c r="AB183" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC183" s="4" t="inlineStr"/>
+      <c r="AC183" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -19708,7 +19812,11 @@
       <c r="AB185" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC185" s="4" t="inlineStr"/>
+      <c r="AC185" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -19809,7 +19917,11 @@
       <c r="AB186" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC186" s="4" t="inlineStr"/>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -21231,7 +21343,11 @@
       <c r="AB200" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC200" s="4" t="inlineStr"/>
+      <c r="AC200" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 59 clubs short</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1423,8 +1423,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4327,8 +4327,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7207,8 +7207,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7922,8 +7922,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -9211,13 +9211,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>4</v>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9784,8 +9784,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -9980,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V90" s="9" t="n">
         <v>0</v>
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14728,8 +14728,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14763,7 +14763,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14812,8 +14812,8 @@
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S137" s="9" t="n">
-        <v>1</v>
+      <c r="S137" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -15834,10 +15834,10 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15939,7 +15939,7 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
@@ -15950,8 +15950,8 @@
       <c r="S148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T148" s="9" t="n">
-        <v>0</v>
+      <c r="T148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U148" s="9" t="n">
         <v>0</v>
@@ -16069,8 +16069,8 @@
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="9" t="n">
         <v>0</v>
@@ -16324,13 +16324,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16662,7 +16662,7 @@
         <v>2</v>
       </c>
       <c r="R155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S155" s="9" t="n">
         <v>1</v>
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17719,8 +17719,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -21058,7 +21058,7 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -21072,13 +21072,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
@@ -21116,8 +21116,8 @@
       <c r="U198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="9" t="n">
-        <v>2</v>
+      <c r="V198" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
@@ -21575,7 +21575,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21740,7 +21740,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -21971,7 +21971,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22433,7 +22433,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22499,7 +22499,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22631,7 +22631,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22895,7 +22895,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 59 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 19 clubs short</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1524,8 +1524,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1629,8 +1629,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2045,8 +2045,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2247,8 +2247,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -4166,13 +4166,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4428,8 +4428,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4533,8 +4533,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5458,8 +5458,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5979,8 +5979,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6185,8 +6185,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6260,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6286,8 +6286,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7720,8 +7720,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8619,8 +8619,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P77" s="9" t="n">
-        <v>3</v>
+      <c r="P77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8859,8 +8859,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -9447,13 +9447,13 @@
         <v>1</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T85" s="9" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9578,8 +9578,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9980,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V90" s="9" t="n">
         <v>0</v>
@@ -9994,8 +9994,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10039,13 +10039,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>5</v>
@@ -10095,8 +10095,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10200,8 +10200,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11230,8 +11230,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11572,7 +11572,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11642,8 +11642,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11743,8 +11743,8 @@
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="9" t="n">
-        <v>0</v>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13807,8 +13807,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13961,13 +13961,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14017,8 +14017,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -14089,7 +14089,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14219,8 +14219,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14425,8 +14425,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14526,8 +14526,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14598,7 +14598,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14627,8 +14627,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15249,8 +15249,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15348,8 +15348,8 @@
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X142" s="9" t="n">
-        <v>3</v>
+      <c r="X142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -15843,7 +15843,7 @@
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" s="9" t="n">
         <v>0</v>
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15912,17 +15912,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15956,11 +15956,11 @@
       <c r="U148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="9" t="n">
-        <v>0</v>
+      <c r="V148" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>5</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16664,8 +16664,8 @@
       <c r="R155" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S155" s="9" t="n">
-        <v>1</v>
+      <c r="S155" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T155" s="10" t="n">
         <v>1</v>
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16825,7 +16825,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16895,8 +16895,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -17031,7 +17031,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -17101,8 +17101,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -17202,8 +17202,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -17338,7 +17338,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17408,8 +17408,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17618,8 +17618,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -17960,7 +17960,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -18030,8 +18030,8 @@
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18967,8 +18967,8 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="10" t="n">
         <v>1</v>
@@ -19226,13 +19226,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>4</v>
       </c>
       <c r="W180" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X180" s="10" t="n">
         <v>5</v>
@@ -19632,7 +19632,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19702,8 +19702,8 @@
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="9" t="n">
-        <v>0</v>
+      <c r="Z184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA184" s="10" t="n">
         <v>1</v>
@@ -19943,7 +19943,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -20013,8 +20013,8 @@
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>0</v>
+      <c r="Z187" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
@@ -20145,7 +20145,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -20215,8 +20215,8 @@
       <c r="Y189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z189" s="9" t="n">
-        <v>0</v>
+      <c r="Z189" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA189" s="10" t="n">
         <v>1</v>
@@ -20351,7 +20351,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20421,8 +20421,8 @@
       <c r="Y191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z191" s="9" t="n">
-        <v>0</v>
+      <c r="Z191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA191" s="10" t="n">
         <v>1</v>
@@ -20452,7 +20452,7 @@
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -20522,8 +20522,8 @@
       <c r="Y192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z192" s="9" t="n">
-        <v>0</v>
+      <c r="Z192" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA192" s="10" t="n">
         <v>1</v>
@@ -20654,7 +20654,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K194" s="4" t="n">
         <v>4</v>
@@ -20724,8 +20724,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -20971,13 +20971,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>0</v>
       </c>
       <c r="V197" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W197" s="9" t="n">
         <v>0</v>
@@ -21163,7 +21163,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -21233,8 +21233,8 @@
       <c r="Y199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z199" s="9" t="n">
-        <v>0</v>
+      <c r="Z199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA199" s="10" t="n">
         <v>1</v>
@@ -21575,7 +21575,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21608,7 +21608,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21740,7 +21740,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21806,7 +21806,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -21839,7 +21839,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21872,7 +21872,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21971,7 +21971,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22037,7 +22037,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22070,7 +22070,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22103,7 +22103,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22202,7 +22202,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -22235,7 +22235,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22367,7 +22367,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22433,7 +22433,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22466,7 +22466,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22499,7 +22499,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22514,7 +22514,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -22565,7 +22565,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22598,7 +22598,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22631,7 +22631,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22730,7 +22730,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -22763,7 +22763,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -22796,7 +22796,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -22829,7 +22829,7 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -22862,7 +22862,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -22895,7 +22895,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 19 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1468,17 +1468,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1573,17 +1573,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1614,11 +1614,11 @@
       <c r="T9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="9" t="n">
-        <v>0</v>
+      <c r="U9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1678,17 +1678,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1884,17 +1884,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-37</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2191,17 +2191,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2527,8 +2527,8 @@
       <c r="P18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="n">
-        <v>1</v>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2914,17 +2914,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3124,17 +3124,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3330,17 +3330,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M26" s="8" t="n">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3479,11 +3479,11 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>3</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3584,11 +3584,11 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>2</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>5</v>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3851,17 +3851,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>3</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>0</v>
@@ -4001,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>2</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4166,13 +4166,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4210,11 +4210,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>1</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>6</v>
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4372,17 +4372,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4784,13 +4784,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4828,11 +4828,11 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>1</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>5</v>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4994,17 +4994,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5095,17 +5095,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5402,17 +5402,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5507,17 +5507,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5612,17 +5612,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5656,8 +5656,8 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>1</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5717,13 +5717,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
         <v>0</v>
@@ -5968,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6028,13 +6028,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6230,17 +6230,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6266,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>0</v>
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6436,13 +6436,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6642,13 +6642,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6743,13 +6743,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6844,17 +6844,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6949,13 +6949,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7181,13 +7181,13 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" s="9" t="n">
         <v>0</v>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7353,17 +7353,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7398,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7458,13 +7458,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7563,13 +7563,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7664,13 +7664,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7765,17 +7765,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7809,8 +7809,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>1</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7866,17 +7866,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7967,13 +7967,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8068,13 +8068,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8110,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="U72" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W72" s="9" t="n">
-        <v>0</v>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W72" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>5</v>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>7</v>
+        <v>-15</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8220,8 +8220,8 @@
       <c r="V73" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W73" s="9" t="n">
-        <v>3</v>
+      <c r="W73" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8278,17 +8278,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8326,7 +8326,7 @@
         <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X74" s="10" t="n">
         <v>4</v>
@@ -8383,13 +8383,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8532,8 +8532,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8593,13 +8593,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8637,8 +8637,8 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>3</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8698,17 +8698,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8803,13 +8803,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8904,13 +8904,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8948,8 +8948,8 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>2</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9106,17 +9106,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9150,8 +9150,8 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>3</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9211,17 +9211,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9316,13 +9316,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9417,13 +9417,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9522,17 +9522,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9566,8 +9566,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>0</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9627,17 +9627,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>16</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9671,8 +9671,8 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>2</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9728,13 +9728,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9772,11 +9772,11 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W88" s="9" t="n">
-        <v>0</v>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9833,13 +9833,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9938,13 +9938,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>1</v>
@@ -10144,17 +10144,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10245,13 +10245,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10346,13 +10346,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10447,13 +10447,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10548,17 +10548,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10653,17 +10653,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10758,13 +10758,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10859,13 +10859,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10964,13 +10964,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11069,17 +11069,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11174,13 +11174,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11275,17 +11275,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11320,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11380,13 +11380,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11586,13 +11586,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11889,17 +11889,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11925,7 +11925,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11934,7 +11934,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11994,13 +11994,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12147,7 +12147,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -12204,13 +12204,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12309,17 +12309,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12336,7 +12336,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12414,17 +12414,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="10" t="n">
         <v>2</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12519,17 +12519,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12563,8 +12563,8 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>3</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12620,13 +12620,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>9</v>
+        <v>-7</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>6</v>
@@ -12725,13 +12725,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12826,13 +12826,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12931,13 +12931,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13032,17 +13032,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -13059,7 +13059,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -13137,13 +13137,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13339,13 +13339,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13444,13 +13444,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13491,8 +13491,8 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>0</v>
+      <c r="W124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>5</v>
@@ -13549,13 +13549,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13650,13 +13650,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13795,8 +13795,8 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>2</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13842,7 +13842,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13856,13 +13856,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13900,11 +13900,11 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>1</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X128" s="10" t="n">
         <v>7</v>
@@ -13961,17 +13961,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -14006,7 +14006,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14062,17 +14062,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -14163,17 +14163,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14268,13 +14268,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14369,13 +14369,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14571,13 +14571,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14616,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14672,17 +14672,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14717,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14763,7 +14763,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14777,13 +14777,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14824,8 +14824,8 @@
       <c r="V137" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W137" s="9" t="n">
-        <v>2</v>
+      <c r="W137" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14882,17 +14882,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14927,7 +14927,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14987,13 +14987,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -15031,11 +15031,11 @@
       <c r="U139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="9" t="n">
-        <v>2</v>
+      <c r="V139" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>4</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15092,13 +15092,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15136,11 +15136,11 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>2</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X140" s="10" t="n">
         <v>4</v>
@@ -15179,7 +15179,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15193,13 +15193,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T141" s="9" t="n">
         <v>0</v>
@@ -15237,11 +15237,11 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W141" s="9" t="n">
-        <v>0</v>
+      <c r="V141" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W141" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>5</v>
@@ -15298,13 +15298,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15399,13 +15399,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15428,8 +15428,8 @@
       <c r="P143" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q143" s="9" t="n">
-        <v>1</v>
+      <c r="Q143" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15605,17 +15605,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15706,13 +15706,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15807,13 +15807,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15912,17 +15912,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15960,7 +15960,7 @@
         <v>4</v>
       </c>
       <c r="W148" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>5</v>
@@ -16013,13 +16013,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -16159,7 +16159,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16324,13 +16324,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16368,8 +16368,8 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>3</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16530,13 +16530,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
@@ -16586,8 +16586,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16629,13 +16629,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16670,11 +16670,11 @@
       <c r="T155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U155" s="9" t="n">
-        <v>0</v>
+      <c r="U155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16839,17 +16839,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16940,13 +16940,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -16984,11 +16984,11 @@
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="9" t="n">
+      <c r="V158" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W158" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W158" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>5</v>
@@ -17146,17 +17146,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17352,17 +17352,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17457,13 +17457,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17562,17 +17562,17 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M164" s="8" t="n">
@@ -17597,8 +17597,8 @@
       <c r="R164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S164" s="9" t="n">
-        <v>1</v>
+      <c r="S164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T164" s="10" t="n">
         <v>1</v>
@@ -17663,17 +17663,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L165" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="8" t="n">
@@ -17764,17 +17764,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -17869,13 +17869,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17974,17 +17974,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -18079,13 +18079,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18285,13 +18285,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -18428,8 +18428,8 @@
       <c r="S172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T172" s="9" t="n">
-        <v>0</v>
+      <c r="T172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U172" s="9" t="n">
         <v>0</v>
@@ -18437,8 +18437,8 @@
       <c r="V172" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W172" s="9" t="n">
-        <v>2</v>
+      <c r="W172" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X172" s="10" t="n">
         <v>6</v>
@@ -18495,13 +18495,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -18596,17 +18596,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L174" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -18701,13 +18701,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
@@ -18806,17 +18806,17 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M176" s="8" t="n">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18911,17 +18911,17 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L177" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M177" s="8" t="n">
@@ -18955,8 +18955,8 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>1</v>
+      <c r="V177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -19016,13 +19016,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19121,13 +19121,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19163,13 +19163,13 @@
         <v>1</v>
       </c>
       <c r="U179" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V179" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="V179" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>6</v>
@@ -19226,13 +19226,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>5</v>
+        <v>-11</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -19331,13 +19331,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>4</v>
       </c>
       <c r="W181" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>6</v>
@@ -19436,13 +19436,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19646,17 +19646,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -19694,7 +19694,7 @@
         <v>4</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X184" s="10" t="n">
         <v>6</v>
@@ -19747,13 +19747,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -19852,13 +19852,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>4</v>
       </c>
       <c r="W186" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X186" s="10" t="n">
         <v>7</v>
@@ -19943,7 +19943,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19957,13 +19957,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -20001,11 +20001,11 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="9" t="n">
-        <v>3</v>
+      <c r="V187" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W187" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X187" s="10" t="n">
         <v>4</v>
@@ -20058,13 +20058,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>0</v>
       </c>
       <c r="V188" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -20159,13 +20159,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>0</v>
       </c>
       <c r="V189" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
@@ -20260,17 +20260,17 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M190" s="8" t="n">
@@ -20305,7 +20305,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20410,7 +20410,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20466,13 +20466,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20567,13 +20567,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -20668,17 +20668,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="8" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>10</v>
@@ -20971,13 +20971,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -21015,11 +21015,11 @@
       <c r="U197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V197" s="9" t="n">
-        <v>3</v>
+      <c r="V197" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W197" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X197" s="10" t="n">
         <v>7</v>
@@ -21072,17 +21072,17 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M198" s="8" t="n">
@@ -21177,13 +21177,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -21278,13 +21278,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
@@ -21322,8 +21322,8 @@
       <c r="U200" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V200" s="9" t="n">
-        <v>1</v>
+      <c r="V200" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W200" s="9" t="n">
         <v>0</v>
@@ -21383,13 +21383,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21590,7 +21590,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -21623,7 +21623,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -21641,7 +21641,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21656,7 +21656,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21689,7 +21689,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -21707,7 +21707,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21722,7 +21722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -21740,7 +21740,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21755,7 +21755,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -21773,7 +21773,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -21788,7 +21788,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21821,7 +21821,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -21839,7 +21839,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21854,7 +21854,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -21887,7 +21887,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -21920,7 +21920,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -21953,7 +21953,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -21971,7 +21971,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -21986,7 +21986,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -22004,13 +22004,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -22019,7 +22019,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -22037,7 +22037,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -22052,7 +22052,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -22070,7 +22070,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22085,7 +22085,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -22103,7 +22103,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22118,7 +22118,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -22151,7 +22151,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -22184,7 +22184,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -22250,7 +22250,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -22268,7 +22268,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -22283,7 +22283,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -22316,7 +22316,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -22334,7 +22334,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22367,7 +22367,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22415,7 +22415,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -22433,7 +22433,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22448,7 +22448,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -22466,7 +22466,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22514,7 +22514,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -22532,7 +22532,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22565,13 +22565,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -22580,7 +22580,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -22598,7 +22598,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22613,7 +22613,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -22646,7 +22646,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -22664,7 +22664,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22712,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -22730,7 +22730,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -22745,7 +22745,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -22778,7 +22778,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -22796,7 +22796,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -22862,7 +22862,7 @@
         <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -22895,7 +22895,7 @@
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -22910,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/71/inyear.xlsx
+++ b/docs/d/71/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 5 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 5 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="10" t="n">
         <v>2</v>
@@ -2536,14 +2536,14 @@
       <c r="S18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>3</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>1</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V33" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="V33" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="W33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>7</v>
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6642,13 +6642,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6844,13 +6844,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7765,13 +7765,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8173,13 +8173,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>7</v>
@@ -8593,13 +8593,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>5</v>
@@ -9316,13 +9316,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9455,8 +9455,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -10174,7 +10174,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -10245,13 +10245,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" s="9" t="n">
         <v>0</v>
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10682,8 +10682,8 @@
       <c r="P97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q97" s="9" t="n">
-        <v>1</v>
+      <c r="Q97" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10964,13 +10964,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11069,17 +11069,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -12620,13 +12620,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>4</v>
       </c>
       <c r="W116" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>6</v>
@@ -12826,13 +12826,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13891,14 +13891,14 @@
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="S128" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V128" s="10" t="n">
         <v>4</v>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14163,13 +14163,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14207,8 +14207,8 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>2</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14268,13 +14268,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14324,8 +14324,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -15298,13 +15298,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15807,13 +15807,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -16013,13 +16013,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>0</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16324,13 +16324,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16629,13 +16629,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16671,10 +16671,10 @@
         <v>1</v>
       </c>
       <c r="U155" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V155" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -16720,7 +16720,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16734,13 +16734,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16778,8 +16778,8 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>3</v>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16940,13 +16940,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -17146,17 +17146,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-15</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17352,13 +17352,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17562,13 +17562,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17974,13 +17974,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -19121,13 +19121,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -19168,8 +19168,8 @@
       <c r="V179" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W179" s="9" t="n">
-        <v>3</v>
+      <c r="W179" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>6</v>
@@ -19317,7 +19317,7 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19331,13 +19331,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19378,8 +19378,8 @@
       <c r="V181" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W181" s="9" t="n">
-        <v>3</v>
+      <c r="W181" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>6</v>
@@ -19646,13 +19646,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>2</v>
       </c>
       <c r="R184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S184" s="9" t="n">
         <v>0</v>
@@ -19747,13 +19747,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>4</v>
       </c>
       <c r="W185" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X185" s="10" t="n">
         <v>6</v>
@@ -19957,13 +19957,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>4</v>
       </c>
       <c r="W187" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X187" s="10" t="n">
         <v>4</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>0</v>
       </c>
       <c r="S190" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190" s="10" t="n">
         <v>1</v>
@@ -20466,13 +20466,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>0</v>
       </c>
       <c r="V192" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W192" s="9" t="n">
         <v>0</v>
@@ -21177,13 +21177,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -21383,13 +21383,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>0</v>
       </c>
       <c r="S201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T201" s="9" t="n">
         <v>0</v>
@@ -21641,13 +21641,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -21740,13 +21740,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -22070,7 +22070,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22169,7 +22169,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22217,7 +22217,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -22367,13 +22367,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22565,7 +22565,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -22613,7 +22613,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -22730,7 +22730,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -22763,7 +22763,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
